--- a/output/roomself_excel/384.xlsx
+++ b/output/roomself_excel/384.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>354806</v>
+        <v>124575</v>
       </c>
       <c r="D2" t="n">
-        <v>5432</v>
+        <v>3024</v>
       </c>
       <c r="E2" t="n">
-        <v>893</v>
+        <v>372</v>
       </c>
       <c r="F2" t="n">
-        <v>811</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>162733</v>
+        <v>162272</v>
       </c>
       <c r="D3" t="n">
-        <v>3256</v>
+        <v>3252</v>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F3" t="n">
         <v>32</v>
@@ -520,7 +520,7 @@
         <v>3508</v>
       </c>
       <c r="E4" t="n">
-        <v>893</v>
+        <v>493</v>
       </c>
       <c r="F4" t="n">
         <v>448</v>
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>69112</v>
+        <v>21646</v>
       </c>
       <c r="D5" t="n">
-        <v>2348</v>
+        <v>1180</v>
       </c>
       <c r="E5" t="n">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>293209</v>
+        <v>33741</v>
       </c>
       <c r="D6" t="n">
-        <v>4800</v>
+        <v>1480</v>
       </c>
       <c r="E6" t="n">
-        <v>894</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>287786</v>
+        <v>23572</v>
       </c>
       <c r="D7" t="n">
-        <v>4800</v>
+        <v>1232</v>
       </c>
       <c r="E7" t="n">
-        <v>894</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>68475</v>
+        <v>75978</v>
       </c>
       <c r="D8" t="n">
-        <v>2320</v>
+        <v>3278</v>
       </c>
       <c r="E8" t="n">
-        <v>445</v>
+        <v>380</v>
       </c>
       <c r="F8" t="n">
-        <v>195</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>146517</v>
+        <v>72681</v>
       </c>
       <c r="D9" t="n">
-        <v>3228</v>
+        <v>3208</v>
       </c>
       <c r="E9" t="n">
-        <v>682</v>
+        <v>379</v>
       </c>
       <c r="F9" t="n">
-        <v>444</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1550</v>
+        <v>126248</v>
       </c>
       <c r="D10" t="n">
-        <v>324</v>
+        <v>2844</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1470</v>
+        <v>139093</v>
       </c>
       <c r="D11" t="n">
-        <v>316</v>
+        <v>2984</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>205070</v>
+        <v>354806</v>
       </c>
       <c r="D12" t="n">
-        <v>5748</v>
+        <v>5432</v>
       </c>
       <c r="E12" t="n">
-        <v>678</v>
+        <v>811</v>
       </c>
       <c r="F12" t="n">
-        <v>437</v>
+        <v>493</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2950</v>
+        <v>461</v>
       </c>
       <c r="D13" t="n">
-        <v>436</v>
+        <v>1389</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2744</v>
+        <v>69112</v>
       </c>
       <c r="D14" t="n">
-        <v>420</v>
+        <v>2348</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>454</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2750</v>
+        <v>293209</v>
       </c>
       <c r="D15" t="n">
-        <v>420</v>
+        <v>4800</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>894</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2989</v>
+        <v>287786</v>
       </c>
       <c r="D16" t="n">
-        <v>440</v>
+        <v>4800</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>894</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>75978</v>
+        <v>68475</v>
       </c>
       <c r="D17" t="n">
-        <v>3278</v>
+        <v>2320</v>
       </c>
       <c r="E17" t="n">
-        <v>624</v>
+        <v>445</v>
       </c>
       <c r="F17" t="n">
-        <v>263</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21646</v>
+        <v>146517</v>
       </c>
       <c r="D18" t="n">
-        <v>1180</v>
+        <v>3228</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>150764</v>
+        <v>1550</v>
       </c>
       <c r="D19" t="n">
-        <v>3840</v>
+        <v>324</v>
       </c>
       <c r="E19" t="n">
-        <v>529</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -862,14 +862,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>33741</v>
+        <v>1470</v>
       </c>
       <c r="D20" t="n">
-        <v>1480</v>
+        <v>316</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27635</v>
+        <v>205070</v>
       </c>
       <c r="D21" t="n">
-        <v>1408</v>
+        <v>5748</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22">
@@ -906,14 +906,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>26644</v>
+        <v>2950</v>
       </c>
       <c r="D22" t="n">
-        <v>1360</v>
+        <v>436</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -928,20 +928,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>72681</v>
+        <v>2744</v>
       </c>
       <c r="D23" t="n">
-        <v>3208</v>
+        <v>420</v>
       </c>
       <c r="E23" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>58359</v>
+        <v>2750</v>
       </c>
       <c r="D24" t="n">
-        <v>2576</v>
+        <v>420</v>
       </c>
       <c r="E24" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>85564</v>
+        <v>2989</v>
       </c>
       <c r="D25" t="n">
-        <v>3224</v>
+        <v>440</v>
       </c>
       <c r="E25" t="n">
-        <v>547</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>32332</v>
+        <v>27635</v>
       </c>
       <c r="D26" t="n">
-        <v>1568</v>
+        <v>1408</v>
       </c>
       <c r="E26" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31742</v>
+        <v>3072</v>
       </c>
       <c r="D27" t="n">
-        <v>1548</v>
+        <v>512</v>
       </c>
       <c r="E27" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1038,20 +1038,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>126248</v>
+        <v>58359</v>
       </c>
       <c r="D28" t="n">
-        <v>2844</v>
+        <v>2576</v>
       </c>
       <c r="E28" t="n">
-        <v>813</v>
+        <v>280</v>
       </c>
       <c r="F28" t="n">
-        <v>36</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>139093</v>
+        <v>85564</v>
       </c>
       <c r="D29" t="n">
-        <v>2984</v>
+        <v>3224</v>
       </c>
       <c r="E29" t="n">
-        <v>807</v>
+        <v>547</v>
       </c>
       <c r="F29" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30">
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>79833</v>
+        <v>26189</v>
       </c>
       <c r="D30" t="n">
-        <v>2768</v>
+        <v>1312</v>
       </c>
       <c r="E30" t="n">
-        <v>449</v>
+        <v>157</v>
       </c>
       <c r="F30" t="n">
-        <v>141</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31">
@@ -1108,16 +1108,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>69962</v>
+        <v>32332</v>
       </c>
       <c r="D31" t="n">
-        <v>2344</v>
+        <v>1568</v>
       </c>
       <c r="E31" t="n">
-        <v>391</v>
+        <v>274</v>
       </c>
       <c r="F31" t="n">
-        <v>148</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
@@ -1130,16 +1130,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>56811</v>
+        <v>31742</v>
       </c>
       <c r="D32" t="n">
-        <v>2696</v>
+        <v>1548</v>
       </c>
       <c r="E32" t="n">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="F32" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -1152,16 +1152,82 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>79833</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2768</v>
+      </c>
+      <c r="E33" t="n">
+        <v>449</v>
+      </c>
+      <c r="F33" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>69962</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2344</v>
+      </c>
+      <c r="E34" t="n">
+        <v>391</v>
+      </c>
+      <c r="F34" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>56811</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2696</v>
+      </c>
+      <c r="E35" t="n">
+        <v>246</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
         <v>51053</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D36" t="n">
         <v>2504</v>
       </c>
-      <c r="E33" t="n">
-        <v>408</v>
-      </c>
-      <c r="F33" t="n">
+      <c r="E36" t="n">
         <v>387</v>
+      </c>
+      <c r="F36" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/384.xlsx
+++ b/output/roomself_excel/384.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3024</v>
       </c>
-      <c r="E2" t="n">
-        <v>372</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>3252</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>352</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>32</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +555,27 @@
       <c r="D4" t="n">
         <v>3508</v>
       </c>
-      <c r="E4" t="n">
-        <v>493</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>448</v>
+        <v>416</v>
+      </c>
+      <c r="G4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>461</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +593,12 @@
       <c r="D5" t="n">
         <v>1180</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +615,12 @@
       <c r="D6" t="n">
         <v>1480</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +637,12 @@
       <c r="D7" t="n">
         <v>1232</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +659,27 @@
       <c r="D8" t="n">
         <v>3278</v>
       </c>
-      <c r="E8" t="n">
-        <v>380</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>263</v>
+        <v>329</v>
+      </c>
+      <c r="G8" t="n">
+        <v>32</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>211</v>
+      </c>
+      <c r="J8" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -629,11 +697,27 @@
       <c r="D9" t="n">
         <v>3208</v>
       </c>
-      <c r="E9" t="n">
-        <v>379</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>253</v>
+        <v>330</v>
+      </c>
+      <c r="G9" t="n">
+        <v>32</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>221</v>
+      </c>
+      <c r="J9" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -651,11 +735,27 @@
       <c r="D10" t="n">
         <v>2844</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>344</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>20</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>344</v>
+      </c>
+      <c r="J10" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -673,11 +773,27 @@
       <c r="D11" t="n">
         <v>2984</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>379</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>20</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>379</v>
+      </c>
+      <c r="J11" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -695,11 +811,27 @@
       <c r="D12" t="n">
         <v>5432</v>
       </c>
-      <c r="E12" t="n">
-        <v>811</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>493</v>
+        <v>779</v>
+      </c>
+      <c r="G12" t="n">
+        <v>32</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>461</v>
+      </c>
+      <c r="J12" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +849,12 @@
       <c r="D13" t="n">
         <v>1389</v>
       </c>
-      <c r="E13" t="n">
-        <v>32</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +871,27 @@
       <c r="D14" t="n">
         <v>2348</v>
       </c>
-      <c r="E14" t="n">
-        <v>454</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>193</v>
+        <v>424</v>
+      </c>
+      <c r="G14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>163</v>
+      </c>
+      <c r="J14" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -761,12 +909,20 @@
       <c r="D15" t="n">
         <v>4800</v>
       </c>
-      <c r="E15" t="n">
-        <v>894</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>366</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="G15" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +939,20 @@
       <c r="D16" t="n">
         <v>4800</v>
       </c>
-      <c r="E16" t="n">
-        <v>894</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>366</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="G16" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,11 +969,27 @@
       <c r="D17" t="n">
         <v>2320</v>
       </c>
-      <c r="E17" t="n">
-        <v>445</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>195</v>
+        <v>415</v>
+      </c>
+      <c r="G17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>165</v>
+      </c>
+      <c r="J17" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -827,12 +1007,20 @@
       <c r="D18" t="n">
         <v>3228</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>383</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>30</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1037,12 @@
       <c r="D19" t="n">
         <v>324</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1059,12 @@
       <c r="D20" t="n">
         <v>316</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,11 +1081,27 @@
       <c r="D21" t="n">
         <v>5748</v>
       </c>
-      <c r="E21" t="n">
-        <v>678</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>147</v>
+        <v>630</v>
+      </c>
+      <c r="G21" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>98</v>
+      </c>
+      <c r="J21" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -915,12 +1119,12 @@
       <c r="D22" t="n">
         <v>436</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1141,12 @@
       <c r="D23" t="n">
         <v>420</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1163,12 @@
       <c r="D24" t="n">
         <v>420</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1185,12 @@
       <c r="D25" t="n">
         <v>440</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1207,12 @@
       <c r="D26" t="n">
         <v>1408</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1229,12 @@
       <c r="D27" t="n">
         <v>512</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,11 +1251,27 @@
       <c r="D28" t="n">
         <v>2576</v>
       </c>
-      <c r="E28" t="n">
-        <v>280</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>150</v>
+        <v>250</v>
+      </c>
+      <c r="G28" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>101</v>
+      </c>
+      <c r="J28" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="29">
@@ -1069,12 +1289,20 @@
       <c r="D29" t="n">
         <v>3224</v>
       </c>
-      <c r="E29" t="n">
-        <v>547</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F29" t="n">
-        <v>67</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="G29" t="n">
+        <v>32</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,12 +1319,20 @@
       <c r="D30" t="n">
         <v>1312</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>157</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>32</v>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1349,20 @@
       <c r="D31" t="n">
         <v>1568</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>274</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>30</v>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1135,12 +1379,20 @@
       <c r="D32" t="n">
         <v>1548</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>269</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>30</v>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1157,11 +1409,27 @@
       <c r="D33" t="n">
         <v>2768</v>
       </c>
-      <c r="E33" t="n">
-        <v>449</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F33" t="n">
-        <v>141</v>
+        <v>428</v>
+      </c>
+      <c r="G33" t="n">
+        <v>36</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>87</v>
+      </c>
+      <c r="J33" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="34">
@@ -1179,11 +1447,27 @@
       <c r="D34" t="n">
         <v>2344</v>
       </c>
-      <c r="E34" t="n">
-        <v>391</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>148</v>
+        <v>350</v>
+      </c>
+      <c r="G34" t="n">
+        <v>37</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>94</v>
+      </c>
+      <c r="J34" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="35">
@@ -1201,11 +1485,27 @@
       <c r="D35" t="n">
         <v>2696</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>246</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>21</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>428</v>
+      </c>
+      <c r="J35" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="36">
@@ -1223,11 +1523,27 @@
       <c r="D36" t="n">
         <v>2504</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>239</v>
+      </c>
+      <c r="G36" t="n">
+        <v>21</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>387</v>
       </c>
-      <c r="F36" t="n">
-        <v>41</v>
+      <c r="J36" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/384.xlsx
+++ b/output/roomself_excel/384.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,46 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -509,6 +549,26 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>169</v>
+      </c>
+      <c r="N2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -539,6 +599,26 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>174</v>
+      </c>
+      <c r="N3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -575,6 +655,38 @@
         <v>461</v>
       </c>
       <c r="J4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>169</v>
+      </c>
+      <c r="N4" t="n">
+        <v>32</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>109</v>
+      </c>
+      <c r="R4" t="n">
         <v>32</v>
       </c>
     </row>
@@ -599,6 +711,14 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -621,6 +741,14 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -643,6 +771,14 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -681,6 +817,38 @@
       <c r="J8" t="n">
         <v>32</v>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>105</v>
+      </c>
+      <c r="N8" t="n">
+        <v>32</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>84</v>
+      </c>
+      <c r="R8" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -719,6 +887,38 @@
       <c r="J9" t="n">
         <v>32</v>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>85</v>
+      </c>
+      <c r="N9" t="n">
+        <v>32</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>102</v>
+      </c>
+      <c r="R9" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -757,6 +957,26 @@
       <c r="J10" t="n">
         <v>19</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>57</v>
+      </c>
+      <c r="N10" t="n">
+        <v>19</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -795,6 +1015,26 @@
       <c r="J11" t="n">
         <v>19</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>59</v>
+      </c>
+      <c r="N11" t="n">
+        <v>19</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -831,6 +1071,38 @@
         <v>461</v>
       </c>
       <c r="J12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>333</v>
+      </c>
+      <c r="N12" t="n">
+        <v>32</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>112</v>
+      </c>
+      <c r="R12" t="n">
         <v>32</v>
       </c>
     </row>
@@ -855,6 +1127,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -893,6 +1173,14 @@
       <c r="J14" t="n">
         <v>30</v>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -923,6 +1211,14 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -953,6 +1249,14 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -991,6 +1295,14 @@
       <c r="J17" t="n">
         <v>30</v>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1021,6 +1333,26 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>222</v>
+      </c>
+      <c r="N18" t="n">
+        <v>30</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1043,6 +1375,14 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1065,6 +1405,14 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1103,6 +1451,26 @@
       <c r="J21" t="n">
         <v>30</v>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>214</v>
+      </c>
+      <c r="N21" t="n">
+        <v>30</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1125,6 +1493,14 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1147,6 +1523,14 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1169,6 +1553,14 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1191,6 +1583,14 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1213,6 +1613,14 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1235,6 +1643,14 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1273,6 +1689,14 @@
       <c r="J28" t="n">
         <v>30</v>
       </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1303,6 +1727,26 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>166</v>
+      </c>
+      <c r="N29" t="n">
+        <v>32</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1333,6 +1777,14 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1363,6 +1815,14 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1393,6 +1853,14 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1431,6 +1899,14 @@
       <c r="J33" t="n">
         <v>21</v>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1469,6 +1945,14 @@
       <c r="J34" t="n">
         <v>41</v>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1507,6 +1991,14 @@
       <c r="J35" t="n">
         <v>19</v>
       </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1545,6 +2037,26 @@
       <c r="J36" t="n">
         <v>19</v>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>50</v>
+      </c>
+      <c r="N36" t="n">
+        <v>19</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
